--- a/Data/FlightPlan/FPL_04SEP26.xlsx
+++ b/Data/FlightPlan/FPL_04SEP26.xlsx
@@ -1352,33 +1352,30 @@
     <t>17:05</t>
   </si>
   <si>
-    <t>VN-A811</t>
+    <t>VN-A812</t>
+  </si>
+  <si>
+    <t>MEL</t>
+  </si>
+  <si>
+    <t>VN-A814</t>
+  </si>
+  <si>
+    <t>KZN</t>
+  </si>
+  <si>
+    <t>VN-A815</t>
+  </si>
+  <si>
+    <t>BNE</t>
+  </si>
+  <si>
+    <t>VN-A816</t>
   </si>
   <si>
     <t>SVO</t>
   </si>
   <si>
-    <t>VN-A812</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>VN-A814</t>
-  </si>
-  <si>
-    <t>KZN</t>
-  </si>
-  <si>
-    <t>VN-A815</t>
-  </si>
-  <si>
-    <t>BNE</t>
-  </si>
-  <si>
-    <t>VN-A816</t>
-  </si>
-  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1403,7 +1400,7 @@
     <t>Total Record(s): 405</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 04, 2026 09:03</t>
+    <t xml:space="preserve">Generated on  Sep 04, 2026 09:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -16214,7 +16211,7 @@
         <v>13</v>
       </c>
       <c r="B476" s="7">
-        <v>8923</v>
+        <v>609</v>
       </c>
       <c t="s" r="C476" s="7">
         <v>14</v>
@@ -16227,23 +16224,21 @@
         <v>330</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>227</v>
-      </c>
-      <c t="s" r="K476" s="7">
-        <v>62</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K476" s="7"/>
       <c r="L476" s="7"/>
       <c t="s" r="M476" s="7">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -16251,7 +16246,7 @@
         <v>13</v>
       </c>
       <c r="B477" s="7">
-        <v>8924</v>
+        <v>81</v>
       </c>
       <c t="s" r="C477" s="7">
         <v>14</v>
@@ -16264,84 +16259,78 @@
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="H477" s="8">
         <v>448</v>
       </c>
-      <c t="s" r="H477" s="8">
-        <v>85</v>
-      </c>
       <c t="s" r="I477" s="7">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>294</v>
-      </c>
-      <c t="s" r="K477" s="7">
-        <v>283</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="K477" s="7"/>
       <c r="L477" s="7"/>
-      <c t="s" r="M477" s="7">
-        <v>51</v>
-      </c>
+      <c r="M477" s="7"/>
     </row>
     <row r="478" ht="14.25" customHeight="1">
-      <c r="A478" s="6"/>
-      <c r="B478" s="7"/>
-      <c r="C478" s="7"/>
+      <c t="s" r="A478" s="6">
+        <v>23</v>
+      </c>
+      <c r="B478" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="C478" s="7">
+        <v>14</v>
+      </c>
       <c r="D478" s="7"/>
-      <c r="E478" s="7"/>
-      <c r="F478" s="7"/>
-      <c r="G478" s="8"/>
-      <c r="H478" s="8"/>
-      <c r="I478" s="7"/>
-      <c r="J478" s="7"/>
+      <c t="s" r="E478" s="7">
+        <v>447</v>
+      </c>
+      <c r="F478" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G478" s="8">
+        <v>448</v>
+      </c>
+      <c t="s" r="H478" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I478" s="7">
+        <v>24</v>
+      </c>
+      <c t="s" r="J478" s="7">
+        <v>333</v>
+      </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c r="M478" s="7"/>
     </row>
     <row r="479" ht="14.25" customHeight="1">
-      <c t="s" r="A479" s="6">
-        <v>13</v>
-      </c>
-      <c r="B479" s="7">
-        <v>609</v>
-      </c>
-      <c t="s" r="C479" s="7">
-        <v>14</v>
-      </c>
+      <c r="A479" s="6"/>
+      <c r="B479" s="7"/>
+      <c r="C479" s="7"/>
       <c r="D479" s="7"/>
-      <c t="s" r="E479" s="7">
-        <v>449</v>
-      </c>
-      <c r="F479" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G479" s="8">
-        <v>50</v>
-      </c>
-      <c t="s" r="H479" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="I479" s="7">
-        <v>25</v>
-      </c>
-      <c t="s" r="J479" s="7">
-        <v>73</v>
-      </c>
+      <c r="E479" s="7"/>
+      <c r="F479" s="7"/>
+      <c r="G479" s="8"/>
+      <c r="H479" s="8"/>
+      <c r="I479" s="7"/>
+      <c r="J479" s="7"/>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
-      <c t="s" r="M479" s="7">
-        <v>215</v>
-      </c>
+      <c r="M479" s="7"/>
     </row>
     <row r="480" ht="15" customHeight="1">
       <c t="s" r="A480" s="6">
         <v>13</v>
       </c>
       <c r="B480" s="7">
-        <v>81</v>
+        <v>5805</v>
       </c>
       <c t="s" r="C480" s="7">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
@@ -16351,16 +16340,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>450</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16368,13 +16357,13 @@
     </row>
     <row r="481" ht="14.25" customHeight="1">
       <c t="s" r="A481" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B481" s="7">
-        <v>82</v>
+        <v>5806</v>
       </c>
       <c t="s" r="C481" s="7">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
@@ -16387,13 +16376,13 @@
         <v>450</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>333</v>
+        <v>172</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16419,10 +16408,10 @@
         <v>13</v>
       </c>
       <c r="B483" s="7">
-        <v>5805</v>
+        <v>83</v>
       </c>
       <c t="s" r="C483" s="7">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
@@ -16432,16 +16421,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>452</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>19</v>
+        <v>280</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
@@ -16452,10 +16441,10 @@
         <v>13</v>
       </c>
       <c r="B484" s="7">
-        <v>5806</v>
+        <v>84</v>
       </c>
       <c t="s" r="C484" s="7">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
@@ -16468,13 +16457,13 @@
         <v>452</v>
       </c>
       <c t="s" r="H484" s="8">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>172</v>
+        <v>294</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16500,7 +16489,7 @@
         <v>13</v>
       </c>
       <c r="B486" s="7">
-        <v>83</v>
+        <v>634</v>
       </c>
       <c t="s" r="C486" s="7">
         <v>14</v>
@@ -16516,13 +16505,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H486" s="8">
-        <v>454</v>
+        <v>85</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
@@ -16533,7 +16522,7 @@
         <v>13</v>
       </c>
       <c r="B487" s="7">
-        <v>84</v>
+        <v>8923</v>
       </c>
       <c t="s" r="C487" s="7">
         <v>14</v>
@@ -16546,109 +16535,135 @@
         <v>330</v>
       </c>
       <c t="s" r="G487" s="8">
+        <v>85</v>
+      </c>
+      <c t="s" r="H487" s="8">
         <v>454</v>
       </c>
-      <c t="s" r="H487" s="8">
-        <v>36</v>
-      </c>
       <c t="s" r="I487" s="7">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c t="s" r="J487" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="K487" s="7">
+        <v>62</v>
+      </c>
+      <c r="L487" s="7"/>
+      <c t="s" r="M487" s="7">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="488" ht="14.25" customHeight="1">
+      <c t="s" r="A488" s="6">
+        <v>13</v>
+      </c>
+      <c r="B488" s="7">
+        <v>8924</v>
+      </c>
+      <c t="s" r="C488" s="7">
+        <v>14</v>
+      </c>
+      <c r="D488" s="7"/>
+      <c t="s" r="E488" s="7">
+        <v>453</v>
+      </c>
+      <c r="F488" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G488" s="8">
+        <v>454</v>
+      </c>
+      <c t="s" r="H488" s="8">
+        <v>85</v>
+      </c>
+      <c t="s" r="I488" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J488" s="7">
         <v>294</v>
       </c>
-      <c r="K487" s="7"/>
-      <c r="L487" s="7"/>
-      <c r="M487" s="7"/>
-    </row>
-    <row r="488" ht="14.25" customHeight="1">
-      <c r="A488" s="6"/>
-      <c r="B488" s="7"/>
-      <c r="C488" s="7"/>
-      <c r="D488" s="7"/>
-      <c r="E488" s="7"/>
-      <c r="F488" s="7"/>
-      <c r="G488" s="8"/>
-      <c r="H488" s="8"/>
-      <c r="I488" s="7"/>
-      <c r="J488" s="7"/>
-      <c r="K488" s="7"/>
+      <c t="s" r="K488" s="7">
+        <v>283</v>
+      </c>
       <c r="L488" s="7"/>
-      <c r="M488" s="7"/>
+      <c t="s" r="M488" s="7">
+        <v>51</v>
+      </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
-      <c t="s" r="A489" s="6">
-        <v>13</v>
-      </c>
-      <c r="B489" s="7">
-        <v>634</v>
-      </c>
-      <c t="s" r="C489" s="7">
-        <v>14</v>
-      </c>
+      <c r="A489" s="6"/>
+      <c r="B489" s="7"/>
+      <c r="C489" s="7"/>
       <c r="D489" s="7"/>
-      <c t="s" r="E489" s="7">
-        <v>455</v>
-      </c>
-      <c r="F489" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G489" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H489" s="8">
-        <v>85</v>
-      </c>
-      <c t="s" r="I489" s="7">
-        <v>89</v>
-      </c>
-      <c t="s" r="J489" s="7">
-        <v>303</v>
-      </c>
+      <c r="E489" s="7"/>
+      <c r="F489" s="7"/>
+      <c r="G489" s="8"/>
+      <c r="H489" s="8"/>
+      <c r="I489" s="7"/>
+      <c r="J489" s="7"/>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c r="M489" s="7"/>
     </row>
     <row r="490" ht="15" customHeight="1">
-      <c r="A490" s="6"/>
-      <c r="B490" s="7"/>
-      <c r="C490" s="7"/>
+      <c t="s" r="A490" s="6">
+        <v>13</v>
+      </c>
+      <c r="B490" s="7">
+        <v>5060</v>
+      </c>
+      <c t="s" r="C490" s="7">
+        <v>14</v>
+      </c>
       <c r="D490" s="7"/>
-      <c r="E490" s="7"/>
-      <c r="F490" s="7"/>
-      <c r="G490" s="8"/>
-      <c r="H490" s="8"/>
-      <c r="I490" s="7"/>
-      <c r="J490" s="7"/>
+      <c t="s" r="E490" s="7">
+        <v>455</v>
+      </c>
+      <c r="F490" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G490" s="8">
+        <v>50</v>
+      </c>
+      <c t="s" r="H490" s="8">
+        <v>456</v>
+      </c>
+      <c t="s" r="I490" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J490" s="7">
+        <v>457</v>
+      </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c r="M490" s="7"/>
     </row>
     <row r="491" ht="14.25" customHeight="1">
       <c t="s" r="A491" s="6">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B491" s="7">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c t="s" r="C491" s="7">
         <v>14</v>
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G491" s="8">
+        <v>456</v>
+      </c>
+      <c t="s" r="H491" s="8">
         <v>50</v>
       </c>
-      <c t="s" r="H491" s="8">
-        <v>457</v>
-      </c>
       <c t="s" r="I491" s="7">
-        <v>94</v>
+        <v>399</v>
       </c>
       <c t="s" r="J491" s="7">
         <v>458</v>
@@ -16658,130 +16673,97 @@
       <c r="M491" s="7"/>
     </row>
     <row r="492" ht="14.25" customHeight="1">
-      <c t="s" r="A492" s="6">
-        <v>23</v>
-      </c>
-      <c r="B492" s="7">
-        <v>5061</v>
-      </c>
-      <c t="s" r="C492" s="7">
-        <v>14</v>
-      </c>
+      <c r="A492" s="6"/>
+      <c r="B492" s="7"/>
+      <c r="C492" s="7"/>
       <c r="D492" s="7"/>
-      <c t="s" r="E492" s="7">
-        <v>456</v>
-      </c>
-      <c r="F492" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G492" s="8">
-        <v>457</v>
-      </c>
-      <c t="s" r="H492" s="8">
-        <v>50</v>
-      </c>
-      <c t="s" r="I492" s="7">
-        <v>399</v>
-      </c>
-      <c t="s" r="J492" s="7">
-        <v>459</v>
-      </c>
+      <c r="E492" s="7"/>
+      <c r="F492" s="7"/>
+      <c r="G492" s="8"/>
+      <c r="H492" s="8"/>
+      <c r="I492" s="7"/>
+      <c r="J492" s="7"/>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
       <c r="M492" s="7"/>
     </row>
     <row r="493" ht="14.25" customHeight="1">
-      <c r="A493" s="6"/>
-      <c r="B493" s="7"/>
-      <c r="C493" s="7"/>
+      <c t="s" r="A493" s="6">
+        <v>13</v>
+      </c>
+      <c r="B493" s="7">
+        <v>86</v>
+      </c>
+      <c t="s" r="C493" s="7">
+        <v>14</v>
+      </c>
       <c r="D493" s="7"/>
-      <c r="E493" s="7"/>
-      <c r="F493" s="7"/>
-      <c r="G493" s="8"/>
-      <c r="H493" s="8"/>
-      <c r="I493" s="7"/>
-      <c r="J493" s="7"/>
+      <c t="s" r="E493" s="7">
+        <v>459</v>
+      </c>
+      <c r="F493" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G493" s="8">
+        <v>460</v>
+      </c>
+      <c t="s" r="H493" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I493" s="7">
+        <v>87</v>
+      </c>
+      <c t="s" r="J493" s="7">
+        <v>92</v>
+      </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
-      <c r="M493" s="7"/>
-    </row>
-    <row r="494" ht="14.25" customHeight="1">
-      <c t="s" r="A494" s="6">
-        <v>13</v>
-      </c>
-      <c r="B494" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="C494" s="7">
-        <v>14</v>
-      </c>
-      <c r="D494" s="7"/>
-      <c t="s" r="E494" s="7">
-        <v>460</v>
-      </c>
-      <c r="F494" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G494" s="8">
+      <c t="s" r="M493" s="7">
         <v>461</v>
       </c>
-      <c t="s" r="H494" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="I494" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J494" s="7">
-        <v>92</v>
-      </c>
-      <c r="K494" s="7"/>
-      <c r="L494" s="7"/>
-      <c t="s" r="M494" s="7">
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c t="s" r="A494" s="9">
         <v>462</v>
       </c>
-    </row>
-    <row r="495" ht="16.5" customHeight="1">
-      <c t="s" r="A495" s="9">
+      <c r="B494" s="9"/>
+      <c r="C494" s="9"/>
+      <c r="D494" s="9"/>
+      <c r="E494" s="9"/>
+      <c r="F494" s="9"/>
+      <c r="G494" s="9"/>
+      <c r="H494" s="9"/>
+      <c r="I494" s="9"/>
+      <c r="J494" s="9"/>
+      <c r="K494" s="9"/>
+      <c r="L494" s="9"/>
+      <c r="M494" s="9"/>
+      <c r="N494" s="9"/>
+      <c r="O494" s="9"/>
+    </row>
+    <row r="495" ht="66" customHeight="1"/>
+    <row r="496" ht="16.5" customHeight="1">
+      <c t="s" r="A496" s="10">
         <v>463</v>
       </c>
-      <c r="B495" s="9"/>
-      <c r="C495" s="9"/>
-      <c r="D495" s="9"/>
-      <c r="E495" s="9"/>
-      <c r="F495" s="9"/>
-      <c r="G495" s="9"/>
-      <c r="H495" s="9"/>
-      <c r="I495" s="9"/>
-      <c r="J495" s="9"/>
-      <c r="K495" s="9"/>
-      <c r="L495" s="9"/>
-      <c r="M495" s="9"/>
-      <c r="N495" s="9"/>
-      <c r="O495" s="9"/>
-    </row>
-    <row r="496" ht="65.25" customHeight="1"/>
-    <row r="497" ht="16.5" customHeight="1">
-      <c t="s" r="A497" s="10">
+      <c r="B496" s="10"/>
+      <c r="C496" s="10"/>
+      <c r="D496" s="10"/>
+      <c r="E496" s="10"/>
+      <c r="F496" s="10"/>
+      <c r="G496" s="10"/>
+      <c r="H496" s="10"/>
+      <c r="I496" s="10"/>
+      <c r="J496" s="10"/>
+      <c r="K496" s="10"/>
+      <c t="s" r="L496" s="11">
         <v>464</v>
       </c>
-      <c r="B497" s="10"/>
-      <c r="C497" s="10"/>
-      <c r="D497" s="10"/>
-      <c r="E497" s="10"/>
-      <c r="F497" s="10"/>
-      <c r="G497" s="10"/>
-      <c r="H497" s="10"/>
-      <c r="I497" s="10"/>
-      <c r="J497" s="10"/>
-      <c r="K497" s="10"/>
-      <c t="s" r="L497" s="11">
-        <v>465</v>
-      </c>
-      <c r="M497" s="11"/>
-      <c r="N497" s="11"/>
+      <c r="M496" s="11"/>
+      <c r="N496" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="984">
+  <mergeCells count="982">
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="D3:O4"/>
@@ -17761,11 +17743,9 @@
     <mergeCell ref="K492:L492"/>
     <mergeCell ref="C493:D493"/>
     <mergeCell ref="K493:L493"/>
-    <mergeCell ref="C494:D494"/>
-    <mergeCell ref="K494:L494"/>
-    <mergeCell ref="A495:O495"/>
-    <mergeCell ref="A497:K497"/>
-    <mergeCell ref="L497:N497"/>
+    <mergeCell ref="A494:O494"/>
+    <mergeCell ref="A496:K496"/>
+    <mergeCell ref="L496:N496"/>
   </mergeCells>
   <pageMargins left="0.196666672825813" right="0.219999998807907" top="0.280000001192093" bottom="0.230000004172325" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/Data/FlightPlan/FPL_04SEP26.xlsx
+++ b/Data/FlightPlan/FPL_04SEP26.xlsx
@@ -542,6 +542,9 @@
     <t>HUI</t>
   </si>
   <si>
+    <t>17:43</t>
+  </si>
+  <si>
     <t>VN-A535</t>
   </si>
   <si>
@@ -575,6 +578,9 @@
     <t>18:05</t>
   </si>
   <si>
+    <t>18:08</t>
+  </si>
+  <si>
     <t>19:05</t>
   </si>
   <si>
@@ -1085,6 +1091,9 @@
     <t>10:19</t>
   </si>
   <si>
+    <t>18:29</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1172,6 +1181,9 @@
     <t>VN-A646</t>
   </si>
   <si>
+    <t>18:03</t>
+  </si>
+  <si>
     <t>PER</t>
   </si>
   <si>
@@ -1241,7 +1253,7 @@
     <t>10:38</t>
   </si>
   <si>
-    <t>17:37</t>
+    <t>17:36</t>
   </si>
   <si>
     <t>20:40</t>
@@ -1316,6 +1328,9 @@
     <t>15:43</t>
   </si>
   <si>
+    <t>17:26</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1433,9 +1448,6 @@
     <t>12:43</t>
   </si>
   <si>
-    <t>17:26</t>
-  </si>
-  <si>
     <t>00:55</t>
   </si>
   <si>
@@ -1592,7 +1604,7 @@
     <t>15:01</t>
   </si>
   <si>
-    <t>18:08</t>
+    <t>18:12</t>
   </si>
   <si>
     <t>VN-A698</t>
@@ -1664,7 +1676,7 @@
     <t>Total Record(s): 405</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 04, 2026 16:22</t>
+    <t xml:space="preserve">Generated on  Sep 04, 2026 16:36</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4421,7 +4433,9 @@
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
+      <c t="s" r="M78" s="7">
+        <v>177</v>
+      </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c t="s" r="A79" s="6">
@@ -4483,7 +4497,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4503,7 +4517,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4518,7 +4532,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4530,15 +4544,15 @@
         <v>102</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4553,7 +4567,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4565,7 +4579,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>141</v>
@@ -4573,7 +4587,7 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4588,7 +4602,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4600,15 +4614,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4623,7 +4637,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4632,17 +4646,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I85" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c t="s" r="M85" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c t="s" r="A86" s="6">
@@ -4656,19 +4672,19 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>135</v>
@@ -4689,7 +4705,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4701,7 +4717,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>80</v>
@@ -4737,7 +4753,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4749,7 +4765,7 @@
         <v>137</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>72</v>
@@ -4757,7 +4773,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4772,7 +4788,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4787,12 +4803,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4807,7 +4823,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4840,7 +4856,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4855,7 +4871,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4888,7 +4904,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4900,15 +4916,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4923,7 +4939,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4958,7 +4974,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4970,10 +4986,10 @@
         <v>102</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4993,7 +5009,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5008,12 +5024,12 @@
         <v>115</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5028,7 +5044,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5040,10 +5056,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5076,7 +5092,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5091,7 +5107,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5111,7 +5127,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5126,12 +5142,12 @@
         <v>171</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5146,7 +5162,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5161,7 +5177,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5181,7 +5197,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5196,7 +5212,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5216,7 +5232,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5231,7 +5247,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5249,7 +5265,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5261,10 +5277,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5297,13 +5313,13 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>16</v>
@@ -5332,7 +5348,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5344,15 +5360,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5367,7 +5383,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5376,13 +5392,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5400,19 +5416,19 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>108</v>
@@ -5448,7 +5464,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5457,10 +5473,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>141</v>
@@ -5483,13 +5499,13 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>16</v>
@@ -5498,12 +5514,12 @@
         <v>158</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5518,7 +5534,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5527,10 +5543,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>51</v>
@@ -5538,7 +5554,7 @@
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5553,19 +5569,19 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>152</v>
@@ -5586,7 +5602,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5601,7 +5617,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5634,7 +5650,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5643,10 +5659,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>126</v>
@@ -5654,7 +5670,7 @@
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5669,13 +5685,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>43</v>
@@ -5689,7 +5705,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5704,7 +5720,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5716,7 +5732,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>114</v>
@@ -5724,7 +5740,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5739,7 +5755,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5748,7 +5764,7 @@
         <v>102</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>72</v>
@@ -5759,7 +5775,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5774,19 +5790,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>146</v>
@@ -5794,7 +5810,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5809,7 +5825,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5842,7 +5858,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5890,7 +5906,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5902,7 +5918,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>160</v>
@@ -5910,7 +5926,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5925,7 +5941,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5937,15 +5953,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5960,7 +5976,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5972,15 +5988,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5995,7 +6011,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6010,7 +6026,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -6043,7 +6059,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6058,12 +6074,12 @@
         <v>154</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6078,7 +6094,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6090,15 +6106,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6113,7 +6129,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6148,7 +6164,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6160,7 +6176,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>25</v>
@@ -6181,7 +6197,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6190,10 +6206,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>68</v>
@@ -6229,7 +6245,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6241,7 +6257,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>30</v>
@@ -6249,7 +6265,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6264,7 +6280,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6279,12 +6295,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6299,7 +6315,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6308,10 +6324,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>41</v>
@@ -6332,22 +6348,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6380,7 +6396,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6395,7 +6411,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6415,7 +6431,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6430,12 +6446,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6450,7 +6466,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6465,7 +6481,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6498,13 +6514,13 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
@@ -6513,12 +6529,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6533,7 +6549,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6548,12 +6564,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6568,7 +6584,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6601,7 +6617,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6610,10 +6626,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>63</v>
@@ -6634,13 +6650,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>43</v>
@@ -6649,7 +6665,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6682,7 +6698,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6697,12 +6713,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6717,7 +6733,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6729,15 +6745,15 @@
         <v>102</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6752,7 +6768,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6785,7 +6801,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6797,10 +6813,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6818,7 +6834,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6830,10 +6846,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6866,7 +6882,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6878,7 +6894,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>110</v>
@@ -6886,7 +6902,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6901,7 +6917,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6916,12 +6932,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6936,7 +6952,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6971,7 +6987,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6986,12 +7002,12 @@
         <v>148</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7006,7 +7022,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7054,7 +7070,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7066,7 +7082,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>114</v>
@@ -7089,7 +7105,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7098,18 +7114,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7124,19 +7140,19 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>152</v>
@@ -7157,7 +7173,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7166,10 +7182,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>26</v>
@@ -7205,7 +7221,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7220,12 +7236,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7240,7 +7256,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7255,12 +7271,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7275,7 +7291,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7287,13 +7303,13 @@
         <v>43</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="K171" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
@@ -7312,7 +7328,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7327,14 +7343,14 @@
         <v>72</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="K172" s="7">
         <v>148</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7349,7 +7365,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7364,7 +7380,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7382,7 +7398,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7394,7 +7410,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>152</v>
@@ -7415,7 +7431,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7427,10 +7443,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7448,7 +7464,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7460,7 +7476,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>121</v>
@@ -7496,7 +7512,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7511,12 +7527,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7531,7 +7547,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7546,12 +7562,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7566,7 +7582,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7578,7 +7594,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>163</v>
@@ -7599,7 +7615,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7611,10 +7627,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7632,7 +7648,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7644,7 +7660,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>18</v>
@@ -7680,7 +7696,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7692,7 +7708,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>126</v>
@@ -7700,7 +7716,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7715,7 +7731,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7735,7 +7751,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7750,7 +7766,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7759,7 +7775,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>140</v>
@@ -7770,7 +7786,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7785,13 +7801,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>43</v>
@@ -7800,12 +7816,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7820,7 +7836,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7829,13 +7845,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7853,22 +7869,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7901,7 +7917,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7910,18 +7926,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7936,13 +7952,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>43</v>
@@ -7951,7 +7967,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7971,7 +7987,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7980,7 +7996,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>49</v>
@@ -8004,22 +8020,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8052,7 +8068,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8061,18 +8077,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8087,13 +8103,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>16</v>
@@ -8102,7 +8118,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -8135,7 +8151,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8144,7 +8160,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>126</v>
@@ -8155,7 +8171,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8170,13 +8186,13 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>43</v>
@@ -8185,12 +8201,12 @@
         <v>112</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8205,7 +8221,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8214,18 +8230,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8240,22 +8256,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8288,7 +8304,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8321,7 +8337,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8333,10 +8349,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8369,7 +8385,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8378,10 +8394,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>154</v>
@@ -8389,7 +8405,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8404,13 +8420,13 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>107</v>
@@ -8419,12 +8435,12 @@
         <v>170</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8439,7 +8455,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8448,18 +8464,18 @@
         <v>107</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8474,19 +8490,19 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>72</v>
@@ -8509,7 +8525,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8521,7 +8537,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>90</v>
@@ -8544,7 +8560,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8556,10 +8572,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="K212" s="7">
         <v>51</v>
@@ -8581,7 +8597,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8593,10 +8609,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8629,7 +8645,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8638,18 +8654,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8664,22 +8680,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8699,7 +8715,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8708,13 +8724,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8734,13 +8750,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>43</v>
@@ -8749,7 +8765,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8767,7 +8783,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8779,10 +8795,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8800,7 +8816,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8812,10 +8828,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8848,7 +8864,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8860,7 +8876,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>44</v>
@@ -8868,7 +8884,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8883,7 +8899,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8895,15 +8911,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8918,7 +8934,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8927,7 +8943,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>48</v>
@@ -8938,7 +8954,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8953,13 +8969,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>43</v>
@@ -8973,7 +8989,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8988,7 +9004,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9036,7 +9052,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9045,7 +9061,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>166</v>
@@ -9056,7 +9072,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9071,13 +9087,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>43</v>
@@ -9091,7 +9107,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9106,7 +9122,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9121,7 +9137,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -9141,7 +9157,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9153,14 +9169,16 @@
         <v>43</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
-      <c r="M231" s="7"/>
+      <c t="s" r="M231" s="7">
+        <v>360</v>
+      </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c t="s" r="A232" s="6">
@@ -9174,7 +9192,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9186,7 +9204,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>65</v>
@@ -9222,7 +9240,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9234,7 +9252,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>157</v>
@@ -9242,7 +9260,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9257,7 +9275,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9266,13 +9284,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9292,22 +9310,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9325,7 +9343,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9337,7 +9355,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>39</v>
@@ -9358,7 +9376,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9367,10 +9385,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>122</v>
@@ -9391,22 +9409,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9439,7 +9457,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9448,10 +9466,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>59</v>
@@ -9459,7 +9477,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9474,19 +9492,19 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>148</v>
@@ -9509,7 +9527,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9524,7 +9542,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9544,7 +9562,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9577,7 +9595,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9586,13 +9604,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9610,13 +9628,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>43</v>
@@ -9658,7 +9676,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9670,7 +9688,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>111</v>
@@ -9678,7 +9696,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9693,7 +9711,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9705,7 +9723,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>59</v>
@@ -9713,7 +9731,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9728,7 +9746,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9743,12 +9761,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9763,7 +9781,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9775,15 +9793,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9798,7 +9816,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9813,7 +9831,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9831,7 +9849,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9843,10 +9861,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9879,7 +9897,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9888,18 +9906,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9914,27 +9932,27 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9949,27 +9967,27 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9984,19 +10002,19 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>152</v>
@@ -10032,7 +10050,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10041,18 +10059,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I260" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10067,22 +10085,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10100,22 +10118,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10133,19 +10151,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>95</v>
@@ -10181,7 +10199,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10196,12 +10214,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10216,7 +10234,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10225,18 +10243,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10251,13 +10269,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>43</v>
@@ -10266,11 +10284,13 @@
         <v>90</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="7"/>
+      <c t="s" r="M267" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c t="s" r="A268" s="6">
@@ -10284,7 +10304,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10293,10 +10313,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>97</v>
@@ -10332,7 +10352,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10347,12 +10367,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10367,7 +10387,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10379,15 +10399,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10402,7 +10422,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10414,15 +10434,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10437,7 +10457,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10470,7 +10490,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10482,10 +10502,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10518,7 +10538,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10530,7 +10550,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>80</v>
@@ -10538,7 +10558,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10553,7 +10573,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10568,12 +10588,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10588,7 +10608,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10600,7 +10620,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>160</v>
@@ -10608,7 +10628,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10623,7 +10643,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10632,7 +10652,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>115</v>
@@ -10643,7 +10663,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10658,19 +10678,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>152</v>
@@ -10691,7 +10711,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10703,7 +10723,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>93</v>
@@ -10739,7 +10759,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10751,15 +10771,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10774,7 +10794,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10789,12 +10809,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10809,7 +10829,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10818,18 +10838,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10844,19 +10864,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>174</v>
@@ -10864,7 +10884,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10879,7 +10899,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10888,18 +10908,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10914,19 +10934,19 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>92</v>
@@ -10934,7 +10954,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10964,7 +10984,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10976,15 +10996,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10999,7 +11019,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11014,7 +11034,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11034,7 +11054,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11046,15 +11066,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11069,7 +11089,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11104,7 +11124,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11116,7 +11136,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>19</v>
@@ -11124,7 +11144,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11139,7 +11159,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11151,15 +11171,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11174,7 +11194,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11186,10 +11206,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11207,7 +11227,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11219,7 +11239,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>164</v>
@@ -11255,7 +11275,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11270,12 +11290,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11290,7 +11310,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11299,13 +11319,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11323,22 +11343,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11371,7 +11391,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11391,7 +11411,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11406,7 +11426,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11441,7 +11461,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11461,7 +11481,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11476,7 +11496,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11488,10 +11508,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11509,7 +11529,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11524,7 +11544,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11542,7 +11562,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11554,7 +11574,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>120</v>
@@ -11590,7 +11610,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11602,7 +11622,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>138</v>
@@ -11610,7 +11630,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11625,7 +11645,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11637,7 +11657,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>87</v>
@@ -11660,7 +11680,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11672,7 +11692,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>30</v>
@@ -11680,7 +11700,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11695,7 +11715,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11707,15 +11727,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11730,7 +11750,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11742,10 +11762,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11763,7 +11783,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11778,7 +11798,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11796,7 +11816,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11805,13 +11825,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11829,22 +11849,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11877,7 +11897,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11892,12 +11912,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11912,7 +11932,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11921,18 +11941,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11947,13 +11967,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>37</v>
@@ -11982,7 +12002,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11997,12 +12017,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12017,7 +12037,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -12032,7 +12052,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12050,7 +12070,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12083,7 +12103,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12095,10 +12115,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12131,7 +12151,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12143,15 +12163,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12166,7 +12186,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12178,7 +12198,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>148</v>
@@ -12201,7 +12221,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12210,10 +12230,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>19</v>
@@ -12221,7 +12241,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12236,26 +12256,28 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>92</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
-      <c r="M330" s="7"/>
+      <c t="s" r="M330" s="7">
+        <v>439</v>
+      </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
       <c t="s" r="A331" s="6">
@@ -12269,7 +12291,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12278,10 +12300,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>165</v>
@@ -12306,22 +12328,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12354,7 +12376,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12369,7 +12391,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12389,7 +12411,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12401,15 +12423,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12424,7 +12446,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12436,7 +12458,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>158</v>
@@ -12444,7 +12466,7 @@
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12459,7 +12481,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12479,7 +12501,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12494,7 +12516,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12506,7 +12528,7 @@
         <v>137</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>146</v>
@@ -12514,7 +12536,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12529,7 +12551,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12544,7 +12566,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12562,7 +12584,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12574,7 +12596,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>18</v>
@@ -12610,7 +12632,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12619,18 +12641,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12645,27 +12667,27 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12680,7 +12702,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12689,10 +12711,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>146</v>
@@ -12713,13 +12735,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>43</v>
@@ -12761,7 +12783,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12770,10 +12792,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>105</v>
@@ -12781,7 +12803,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12796,13 +12818,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>43</v>
@@ -12811,12 +12833,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12831,7 +12853,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12840,18 +12862,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12866,19 +12888,19 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>158</v>
@@ -12886,7 +12908,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12901,7 +12923,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12910,18 +12932,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12936,19 +12958,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>93</v>
@@ -12984,7 +13006,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12993,13 +13015,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13019,13 +13041,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>43</v>
@@ -13052,7 +13074,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13064,10 +13086,10 @@
         <v>176</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13085,7 +13107,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13097,10 +13119,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13133,7 +13155,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13148,12 +13170,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13168,7 +13190,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13180,7 +13202,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>160</v>
@@ -13188,7 +13210,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13203,7 +13225,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13215,15 +13237,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13238,7 +13260,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13250,10 +13272,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -13286,7 +13308,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13295,18 +13317,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13321,27 +13343,27 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13356,7 +13378,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13368,7 +13390,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>98</v>
@@ -13376,7 +13398,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13391,7 +13413,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13406,12 +13428,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13441,7 +13463,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13450,10 +13472,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>158</v>
@@ -13461,7 +13483,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13476,13 +13498,13 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>16</v>
@@ -13496,7 +13518,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13511,7 +13533,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13523,7 +13545,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>35</v>
@@ -13531,7 +13553,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13546,7 +13568,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13558,7 +13580,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>118</v>
@@ -13579,7 +13601,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13588,13 +13610,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13612,13 +13634,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>16</v>
@@ -13627,7 +13649,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13660,7 +13682,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13678,11 +13700,11 @@
         <v>140</v>
       </c>
       <c t="s" r="K376" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13697,7 +13719,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13706,10 +13728,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>92</v>
@@ -13732,22 +13754,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13765,7 +13787,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13777,10 +13799,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13813,7 +13835,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13825,7 +13847,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>110</v>
@@ -13833,7 +13855,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13848,7 +13870,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13860,10 +13882,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13883,7 +13905,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13892,18 +13914,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13918,13 +13940,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>16</v>
@@ -13933,7 +13955,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13953,7 +13975,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13962,18 +13984,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>474</v>
+        <v>439</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13988,13 +14010,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>16</v>
@@ -14021,7 +14043,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14033,10 +14055,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14069,7 +14091,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14078,18 +14100,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14104,13 +14126,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
@@ -14124,7 +14146,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14139,7 +14161,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14174,7 +14196,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14194,7 +14216,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14209,7 +14231,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14224,7 +14246,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14242,7 +14264,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14254,7 +14276,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>40</v>
@@ -14290,7 +14312,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14299,10 +14321,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>130</v>
@@ -14310,7 +14332,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14325,19 +14347,19 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>35</v>
@@ -14345,7 +14367,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14360,19 +14382,19 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>64</v>
@@ -14393,19 +14415,19 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>40</v>
@@ -14441,7 +14463,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14456,12 +14478,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14476,7 +14498,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14496,7 +14518,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14511,7 +14533,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14520,18 +14542,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14546,13 +14568,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>43</v>
@@ -14594,7 +14616,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -14603,18 +14625,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14629,27 +14651,27 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14664,27 +14686,27 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14699,13 +14721,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>16</v>
@@ -14714,12 +14736,12 @@
         <v>30</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14734,7 +14756,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14767,7 +14789,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14782,7 +14804,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14815,7 +14837,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14827,15 +14849,15 @@
         <v>102</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14850,7 +14872,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14862,7 +14884,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>160</v>
@@ -14885,7 +14907,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14897,7 +14919,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>118</v>
@@ -14918,7 +14940,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14930,10 +14952,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14966,7 +14988,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14978,7 +15000,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>55</v>
@@ -15001,7 +15023,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15013,15 +15035,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15036,7 +15058,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15048,15 +15070,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15071,7 +15093,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15086,12 +15108,12 @@
         <v>158</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15106,7 +15128,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15115,7 +15137,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>150</v>
@@ -15126,7 +15148,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15141,13 +15163,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
@@ -15156,7 +15178,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15174,7 +15196,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15183,10 +15205,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>18</v>
@@ -15222,7 +15244,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15234,15 +15256,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15257,7 +15279,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15266,10 +15288,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>130</v>
@@ -15292,27 +15314,27 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15327,7 +15349,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15336,7 +15358,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>75</v>
@@ -15360,22 +15382,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15408,13 +15430,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
+        <v>509</v>
+      </c>
+      <c r="F432" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G432" s="8">
         <v>505</v>
-      </c>
-      <c r="F432" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G432" s="8">
-        <v>501</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>16</v>
@@ -15423,12 +15445,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15443,7 +15465,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15452,13 +15474,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>143</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15478,22 +15500,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15511,7 +15533,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15523,10 +15545,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15559,7 +15581,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15568,7 +15590,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>80</v>
@@ -15579,7 +15601,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15594,13 +15616,13 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>37</v>
@@ -15609,12 +15631,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15629,7 +15651,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15638,18 +15660,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15664,22 +15686,22 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15697,7 +15719,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15709,7 +15731,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>108</v>
@@ -15745,7 +15767,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15754,13 +15776,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15780,19 +15802,19 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>21</v>
@@ -15800,7 +15822,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15815,7 +15837,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -15830,7 +15852,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15848,7 +15870,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15860,10 +15882,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15881,7 +15903,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15893,7 +15915,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>120</v>
@@ -15914,7 +15936,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15926,10 +15948,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15962,7 +15984,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15974,15 +15996,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -15997,7 +16019,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16006,10 +16028,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>157</v>
@@ -16017,7 +16039,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16032,13 +16054,13 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>43</v>
@@ -16047,12 +16069,12 @@
         <v>139</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16067,7 +16089,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16079,15 +16101,15 @@
         <v>131</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16102,7 +16124,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16114,28 +16136,46 @@
         <v>43</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>214</v>
+        <v>33</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
-      <c r="A455" s="6"/>
-      <c r="B455" s="7"/>
-      <c r="C455" s="7"/>
+      <c t="s" r="A455" s="6">
+        <v>13</v>
+      </c>
+      <c r="B455" s="7">
+        <v>805</v>
+      </c>
+      <c t="s" r="C455" s="7">
+        <v>14</v>
+      </c>
       <c r="D455" s="7"/>
-      <c r="E455" s="7"/>
-      <c r="F455" s="7"/>
-      <c r="G455" s="8"/>
-      <c r="H455" s="8"/>
-      <c r="I455" s="7"/>
-      <c r="J455" s="7"/>
+      <c t="s" r="E455" s="7">
+        <v>518</v>
+      </c>
+      <c r="F455" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G455" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="H455" s="8">
+        <v>137</v>
+      </c>
+      <c t="s" r="I455" s="7">
+        <v>378</v>
+      </c>
+      <c t="s" r="J455" s="7">
+        <v>36</v>
+      </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c r="M455" s="7"/>
@@ -16145,84 +16185,62 @@
         <v>13</v>
       </c>
       <c r="B456" s="7">
-        <v>226</v>
+        <v>806</v>
       </c>
       <c t="s" r="C456" s="7">
         <v>14</v>
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F456" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>333</v>
+        <v>43</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>18</v>
+        <v>330</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
-      <c t="s" r="M456" s="7">
-        <v>521</v>
-      </c>
+      <c r="M456" s="7"/>
     </row>
     <row r="457" ht="14.25" customHeight="1">
-      <c t="s" r="A457" s="6">
-        <v>13</v>
-      </c>
-      <c r="B457" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="C457" s="7">
-        <v>14</v>
-      </c>
+      <c r="A457" s="6"/>
+      <c r="B457" s="7"/>
+      <c r="C457" s="7"/>
       <c r="D457" s="7"/>
-      <c t="s" r="E457" s="7">
-        <v>520</v>
-      </c>
-      <c r="F457" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G457" s="8">
-        <v>333</v>
-      </c>
-      <c t="s" r="H457" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="I457" s="7">
-        <v>422</v>
-      </c>
-      <c t="s" r="J457" s="7">
-        <v>98</v>
-      </c>
+      <c r="E457" s="7"/>
+      <c r="F457" s="7"/>
+      <c r="G457" s="8"/>
+      <c r="H457" s="8"/>
+      <c r="I457" s="7"/>
+      <c r="J457" s="7"/>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
-      <c t="s" r="M457" s="7">
-        <v>522</v>
-      </c>
+      <c r="M457" s="7"/>
     </row>
     <row r="458" ht="14.25" customHeight="1">
       <c t="s" r="A458" s="6">
         <v>13</v>
       </c>
       <c r="B458" s="7">
-        <v>860</v>
+        <v>226</v>
       </c>
       <c t="s" r="C458" s="7">
         <v>14</v>
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
@@ -16231,18 +16249,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>114</v>
+        <v>373</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>312</v>
+        <v>525</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16250,132 +16268,132 @@
         <v>13</v>
       </c>
       <c r="B459" s="7">
-        <v>861</v>
+        <v>225</v>
       </c>
       <c t="s" r="C459" s="7">
         <v>14</v>
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
-      <c r="M459" s="7"/>
+      <c t="s" r="M459" s="7">
+        <v>526</v>
+      </c>
     </row>
     <row r="460" ht="15" customHeight="1">
-      <c r="A460" s="6"/>
-      <c r="B460" s="7"/>
-      <c r="C460" s="7"/>
+      <c t="s" r="A460" s="6">
+        <v>13</v>
+      </c>
+      <c r="B460" s="7">
+        <v>860</v>
+      </c>
+      <c t="s" r="C460" s="7">
+        <v>14</v>
+      </c>
       <c r="D460" s="7"/>
-      <c r="E460" s="7"/>
-      <c r="F460" s="7"/>
-      <c r="G460" s="8"/>
-      <c r="H460" s="8"/>
-      <c r="I460" s="7"/>
-      <c r="J460" s="7"/>
+      <c t="s" r="E460" s="7">
+        <v>524</v>
+      </c>
+      <c r="F460" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G460" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="H460" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="I460" s="7">
+        <v>114</v>
+      </c>
+      <c t="s" r="J460" s="7">
+        <v>163</v>
+      </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
-      <c r="M460" s="7"/>
+      <c t="s" r="M460" s="7">
+        <v>314</v>
+      </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
       <c t="s" r="A461" s="6">
         <v>13</v>
       </c>
       <c r="B461" s="7">
-        <v>392</v>
+        <v>861</v>
       </c>
       <c t="s" r="C461" s="7">
         <v>14</v>
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>105</v>
+        <v>429</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
-      <c t="s" r="M461" s="7">
-        <v>524</v>
-      </c>
+      <c r="M461" s="7"/>
     </row>
     <row r="462" ht="14.25" customHeight="1">
-      <c t="s" r="A462" s="6">
-        <v>13</v>
-      </c>
-      <c r="B462" s="7">
-        <v>393</v>
-      </c>
-      <c t="s" r="C462" s="7">
-        <v>14</v>
-      </c>
+      <c r="A462" s="6"/>
+      <c r="B462" s="7"/>
+      <c r="C462" s="7"/>
       <c r="D462" s="7"/>
-      <c t="s" r="E462" s="7">
-        <v>523</v>
-      </c>
-      <c r="F462" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G462" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H462" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="I462" s="7">
-        <v>178</v>
-      </c>
-      <c t="s" r="J462" s="7">
-        <v>86</v>
-      </c>
+      <c r="E462" s="7"/>
+      <c r="F462" s="7"/>
+      <c r="G462" s="8"/>
+      <c r="H462" s="8"/>
+      <c r="I462" s="7"/>
+      <c r="J462" s="7"/>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
-      <c t="s" r="M462" s="7">
-        <v>525</v>
-      </c>
+      <c r="M462" s="7"/>
     </row>
     <row r="463" ht="14.25" customHeight="1">
       <c t="s" r="A463" s="6">
         <v>13</v>
       </c>
       <c r="B463" s="7">
-        <v>274</v>
+        <v>392</v>
       </c>
       <c t="s" r="C463" s="7">
         <v>14</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16384,18 +16402,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>229</v>
+        <v>31</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>238</v>
+        <v>528</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16403,34 +16421,34 @@
         <v>13</v>
       </c>
       <c r="B464" s="7">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c t="s" r="C464" s="7">
         <v>14</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>229</v>
+        <v>31</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -16438,14 +16456,14 @@
         <v>13</v>
       </c>
       <c r="B465" s="7">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c t="s" r="C465" s="7">
         <v>14</v>
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16454,138 +16472,138 @@
         <v>43</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="466" ht="14.25" customHeight="1">
+      <c t="s" r="A466" s="6">
+        <v>13</v>
+      </c>
+      <c r="B466" s="7">
+        <v>275</v>
+      </c>
+      <c t="s" r="C466" s="7">
+        <v>14</v>
+      </c>
+      <c r="D466" s="7"/>
+      <c t="s" r="E466" s="7">
         <v>527</v>
       </c>
-    </row>
-    <row r="466" ht="14.25" customHeight="1">
-      <c r="A466" s="6"/>
-      <c r="B466" s="7"/>
-      <c r="C466" s="7"/>
-      <c r="D466" s="7"/>
-      <c r="E466" s="7"/>
-      <c r="F466" s="7"/>
-      <c r="G466" s="8"/>
-      <c r="H466" s="8"/>
-      <c r="I466" s="7"/>
-      <c r="J466" s="7"/>
+      <c r="F466" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G466" s="8">
+        <v>231</v>
+      </c>
+      <c t="s" r="H466" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="I466" s="7">
+        <v>158</v>
+      </c>
+      <c t="s" r="J466" s="7">
+        <v>115</v>
+      </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
-      <c r="M466" s="7"/>
+      <c t="s" r="M466" s="7">
+        <v>530</v>
+      </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
       <c t="s" r="A467" s="6">
         <v>13</v>
       </c>
       <c r="B467" s="7">
-        <v>581</v>
+        <v>144</v>
       </c>
       <c t="s" r="C467" s="7">
         <v>14</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
-      <c t="s" r="A468" s="6">
-        <v>13</v>
-      </c>
-      <c r="B468" s="7">
-        <v>730</v>
-      </c>
-      <c t="s" r="C468" s="7">
-        <v>14</v>
-      </c>
+      <c r="A468" s="6"/>
+      <c r="B468" s="7"/>
+      <c r="C468" s="7"/>
       <c r="D468" s="7"/>
-      <c t="s" r="E468" s="7">
-        <v>528</v>
-      </c>
-      <c r="F468" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G468" s="8">
-        <v>58</v>
-      </c>
-      <c t="s" r="H468" s="8">
-        <v>229</v>
-      </c>
-      <c t="s" r="I468" s="7">
-        <v>181</v>
-      </c>
-      <c t="s" r="J468" s="7">
-        <v>377</v>
-      </c>
+      <c r="E468" s="7"/>
+      <c r="F468" s="7"/>
+      <c r="G468" s="8"/>
+      <c r="H468" s="8"/>
+      <c r="I468" s="7"/>
+      <c r="J468" s="7"/>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
-      <c t="s" r="M468" s="7">
-        <v>324</v>
-      </c>
+      <c r="M468" s="7"/>
     </row>
     <row r="469" ht="14.25" customHeight="1">
       <c t="s" r="A469" s="6">
         <v>13</v>
       </c>
       <c r="B469" s="7">
-        <v>731</v>
+        <v>581</v>
       </c>
       <c t="s" r="C469" s="7">
         <v>14</v>
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>373</v>
+        <v>223</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16593,14 +16611,14 @@
         <v>13</v>
       </c>
       <c r="B470" s="7">
-        <v>780</v>
+        <v>730</v>
       </c>
       <c t="s" r="C470" s="7">
         <v>14</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -16609,120 +16627,120 @@
         <v>58</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>264</v>
+        <v>182</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>227</v>
-      </c>
-      <c t="s" r="K470" s="7">
-        <v>135</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
-      <c r="A471" s="6"/>
-      <c r="B471" s="7"/>
-      <c r="C471" s="7"/>
+      <c t="s" r="A471" s="6">
+        <v>13</v>
+      </c>
+      <c r="B471" s="7">
+        <v>731</v>
+      </c>
+      <c t="s" r="C471" s="7">
+        <v>14</v>
+      </c>
       <c r="D471" s="7"/>
-      <c r="E471" s="7"/>
-      <c r="F471" s="7"/>
-      <c r="G471" s="8"/>
-      <c r="H471" s="8"/>
-      <c r="I471" s="7"/>
-      <c r="J471" s="7"/>
+      <c t="s" r="E471" s="7">
+        <v>532</v>
+      </c>
+      <c r="F471" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G471" s="8">
+        <v>231</v>
+      </c>
+      <c t="s" r="H471" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="I471" s="7">
+        <v>305</v>
+      </c>
+      <c t="s" r="J471" s="7">
+        <v>376</v>
+      </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
-      <c r="M471" s="7"/>
+      <c t="s" r="M471" s="7">
+        <v>534</v>
+      </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
       <c t="s" r="A472" s="6">
         <v>13</v>
       </c>
       <c r="B472" s="7">
-        <v>125</v>
+        <v>780</v>
       </c>
       <c t="s" r="C472" s="7">
         <v>14</v>
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F472" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G472" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="H472" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H472" s="8">
-        <v>43</v>
-      </c>
       <c t="s" r="I472" s="7">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>336</v>
-      </c>
-      <c r="K472" s="7"/>
+        <v>229</v>
+      </c>
+      <c t="s" r="K472" s="7">
+        <v>135</v>
+      </c>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>45</v>
+        <v>343</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
-      <c t="s" r="A473" s="6">
-        <v>13</v>
-      </c>
-      <c r="B473" s="7">
-        <v>128</v>
-      </c>
-      <c t="s" r="C473" s="7">
-        <v>14</v>
-      </c>
+      <c r="A473" s="6"/>
+      <c r="B473" s="7"/>
+      <c r="C473" s="7"/>
       <c r="D473" s="7"/>
-      <c t="s" r="E473" s="7">
-        <v>531</v>
-      </c>
-      <c r="F473" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G473" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="H473" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I473" s="7">
-        <v>284</v>
-      </c>
-      <c t="s" r="J473" s="7">
-        <v>199</v>
-      </c>
+      <c r="E473" s="7"/>
+      <c r="F473" s="7"/>
+      <c r="G473" s="8"/>
+      <c r="H473" s="8"/>
+      <c r="I473" s="7"/>
+      <c r="J473" s="7"/>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
-      <c t="s" r="M473" s="7">
-        <v>532</v>
-      </c>
+      <c r="M473" s="7"/>
     </row>
     <row r="474" ht="14.25" customHeight="1">
       <c t="s" r="A474" s="6">
         <v>13</v>
       </c>
       <c r="B474" s="7">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c t="s" r="C474" s="7">
         <v>14</v>
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F474" s="7">
         <v>320</v>
@@ -16734,15 +16752,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>519</v>
+        <v>338</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>201</v>
+        <v>45</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -16750,14 +16768,14 @@
         <v>13</v>
       </c>
       <c r="B475" s="7">
-        <v>805</v>
+        <v>128</v>
       </c>
       <c t="s" r="C475" s="7">
         <v>14</v>
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F475" s="7">
         <v>320</v>
@@ -16766,50 +16784,54 @@
         <v>43</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>375</v>
+        <v>286</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>36</v>
+        <v>201</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
-      <c r="M475" s="7"/>
+      <c t="s" r="M475" s="7">
+        <v>536</v>
+      </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
       <c t="s" r="A476" s="6">
         <v>13</v>
       </c>
       <c r="B476" s="7">
-        <v>806</v>
+        <v>143</v>
       </c>
       <c t="s" r="C476" s="7">
         <v>14</v>
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F476" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>328</v>
+        <v>523</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
-      <c r="M476" s="7"/>
+      <c t="s" r="M476" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
       <c r="A477" s="6"/>
@@ -16838,7 +16860,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -16858,7 +16880,7 @@
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -16873,7 +16895,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -16882,18 +16904,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -16908,13 +16930,13 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>43</v>
@@ -16923,7 +16945,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16956,7 +16978,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -16965,7 +16987,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H482" s="8">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c t="s" r="I482" s="7">
         <v>45</v>
@@ -16976,7 +16998,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -16991,13 +17013,13 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>58</v>
@@ -17039,7 +17061,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F485" s="7">
         <v>330</v>
@@ -17048,7 +17070,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>98</v>
@@ -17059,7 +17081,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -17074,13 +17096,13 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>43</v>
@@ -17089,7 +17111,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
@@ -17122,7 +17144,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
@@ -17137,7 +17159,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -17157,7 +17179,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
@@ -17166,20 +17188,20 @@
         <v>37</v>
       </c>
       <c t="s" r="H489" s="8">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c t="s" r="I489" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="K489" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -17194,13 +17216,13 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G490" s="8">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c t="s" r="H490" s="8">
         <v>37</v>
@@ -17209,7 +17231,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="K490" s="7">
         <v>103</v>
@@ -17246,7 +17268,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F492" s="7">
         <v>330</v>
@@ -17255,13 +17277,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H492" s="8">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c t="s" r="I492" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
@@ -17279,22 +17301,22 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F493" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G493" s="8">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c t="s" r="H493" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -17327,13 +17349,13 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>43</v>
@@ -17342,17 +17364,17 @@
         <v>98</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
       <c t="s" r="M495" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c t="s" r="A496" s="9">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
@@ -17372,7 +17394,7 @@
     <row r="497" ht="65.25" customHeight="1"/>
     <row r="498" ht="16.5" customHeight="1">
       <c t="s" r="A498" s="10">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B498" s="10"/>
       <c r="C498" s="10"/>
@@ -17385,7 +17407,7 @@
       <c r="J498" s="10"/>
       <c r="K498" s="10"/>
       <c t="s" r="L498" s="11">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M498" s="11"/>
       <c r="N498" s="11"/>
